--- a/data/GreatLink/GreatLink Dynamic Balanced Portfolio.xlsx
+++ b/data/GreatLink/GreatLink Dynamic Balanced Portfolio.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid203533"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid658203"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,114 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>0.943</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>0.937</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>0.931</t>
+  </si>
+  <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>0.935</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>0.933</t>
+  </si>
+  <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>0.948</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>0.955</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>0.953</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>0.952</t>
+  </si>
+  <si>
     <t>04/11/2025</t>
   </si>
   <si>
-    <t>0.952</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>03/11/2025</t>
   </si>
   <si>
@@ -50,9 +149,6 @@
     <t>30/10/2025</t>
   </si>
   <si>
-    <t>0.955</t>
-  </si>
-  <si>
     <t>29/10/2025</t>
   </si>
   <si>
@@ -81,9 +177,6 @@
   </si>
   <si>
     <t>21/10/2025</t>
-  </si>
-  <si>
-    <t>0.948</t>
   </si>
   <si>
     <t>17/10/2025</t>
@@ -448,7 +541,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -456,10 +549,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -467,10 +560,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -478,10 +571,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -489,10 +582,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -500,10 +593,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -511,10 +604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -558,7 +651,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -566,10 +659,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -577,12 +670,243 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
         <v>5</v>
       </c>
     </row>
